--- a/artfynd/A 1647-2025 artfynd.xlsx
+++ b/artfynd/A 1647-2025 artfynd.xlsx
@@ -795,12 +795,7 @@
         <v>90474077</v>
       </c>
       <c r="B3" t="n">
-        <v>95522</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97451</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>309072.1123270589</v>
+        <v>309072</v>
       </c>
       <c r="R3" t="n">
-        <v>6487684.772266903</v>
+        <v>6487685</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -865,19 +860,9 @@
           <t>1993-07-25</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1993-07-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 1647-2025 artfynd.xlsx
+++ b/artfynd/A 1647-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>90474077</v>
       </c>
       <c r="B3" t="n">
-        <v>97451</v>
+        <v>97457</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 1647-2025 artfynd.xlsx
+++ b/artfynd/A 1647-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>90474077</v>
       </c>
       <c r="B3" t="n">
-        <v>97457</v>
+        <v>97463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Evastina Blomgren, Lisbeth Richter-Pedersén</t>
+          <t>Lisbeth Richter-Pedersén, Evastina Blomgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 1647-2025 artfynd.xlsx
+++ b/artfynd/A 1647-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>90474077</v>
       </c>
       <c r="B3" t="n">
-        <v>97463</v>
+        <v>97465</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lisbeth Richter-Pedersén, Evastina Blomgren</t>
+          <t>Evastina Blomgren, Lisbeth Richter-Pedersén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 1647-2025 artfynd.xlsx
+++ b/artfynd/A 1647-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>90474077</v>
       </c>
       <c r="B3" t="n">
-        <v>97465</v>
+        <v>97466</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 1647-2025 artfynd.xlsx
+++ b/artfynd/A 1647-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>90474077</v>
       </c>
       <c r="B3" t="n">
-        <v>97466</v>
+        <v>97493</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 1647-2025 artfynd.xlsx
+++ b/artfynd/A 1647-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>90474077</v>
       </c>
       <c r="B3" t="n">
-        <v>97493</v>
+        <v>97499</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Evastina Blomgren, Lisbeth Richter-Pedersén</t>
+          <t>Lisbeth Richter-Pedersén, Evastina Blomgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 1647-2025 artfynd.xlsx
+++ b/artfynd/A 1647-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>90474077</v>
       </c>
       <c r="B3" t="n">
-        <v>97499</v>
+        <v>97506</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lisbeth Richter-Pedersén, Evastina Blomgren</t>
+          <t>Evastina Blomgren, Lisbeth Richter-Pedersén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 1647-2025 artfynd.xlsx
+++ b/artfynd/A 1647-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>90474077</v>
       </c>
       <c r="B3" t="n">
-        <v>97506</v>
+        <v>97510</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 1647-2025 artfynd.xlsx
+++ b/artfynd/A 1647-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>90474077</v>
       </c>
       <c r="B3" t="n">
-        <v>97510</v>
+        <v>97517</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 1647-2025 artfynd.xlsx
+++ b/artfynd/A 1647-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>90474077</v>
       </c>
       <c r="B3" t="n">
-        <v>97520</v>
+        <v>97525</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 1647-2025 artfynd.xlsx
+++ b/artfynd/A 1647-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>4240817</v>
       </c>
       <c r="B2" t="n">
-        <v>95521</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97986</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>309067.1472218134</v>
+        <v>309067</v>
       </c>
       <c r="R2" t="n">
-        <v>6487679.778133933</v>
+        <v>6487680</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1993-07-25</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1993-07-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,112 +774,6 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>90474077</v>
-      </c>
-      <c r="B3" t="n">
-        <v>97525</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>221946</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Mattlummer</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Lycopodium clavatum</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>NO om Stenarna, Bergsätra, Boh</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>309072</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6487685</v>
-      </c>
-      <c r="S3" t="n">
-        <v>100</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Munkedal</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Bohuslän</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Foss</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>1993-07-25</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>1993-07-25</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Bohusläns flora - 2011.</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Evastina Blomgren</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Evastina Blomgren, Lisbeth Richter-Pedersén</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Bohusläns Flora 2011</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1647-2025 artfynd.xlsx
+++ b/artfynd/A 1647-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,8 +779,16 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4240817</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>